--- a/calibration_plots/plot_data_glass_rf.xlsx
+++ b/calibration_plots/plot_data_glass_rf.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -368,50 +368,42 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0.3941666666666667</v>
+        <v>0.4084186046511628</v>
       </c>
       <c r="B2">
-        <v>0.6388888888888888</v>
+        <v>0.6279069767441861</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.5223333333333333</v>
+        <v>0.5575348837209302</v>
       </c>
       <c r="B3">
-        <v>0.6111111111111112</v>
+        <v>0.6511627906976745</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.6343428571428571</v>
+        <v>0.6857619047619048</v>
       </c>
       <c r="B4">
-        <v>0.6571428571428571</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.7394444444444445</v>
+        <v>0.8050697674418604</v>
       </c>
       <c r="B5">
-        <v>0.8611111111111112</v>
+        <v>0.9767441860465116</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.8418333333333333</v>
+        <v>0.946</v>
       </c>
       <c r="B6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7">
-        <v>0.9574857142857143</v>
-      </c>
-      <c r="B7">
-        <v>0.9428571428571428</v>
+        <v>0.9534883720930233</v>
       </c>
     </row>
   </sheetData>
